--- a/MainApp/Source/Layouts/BlockNonSatisfactoryItems.xlsx
+++ b/MainApp/Source/Layouts/BlockNonSatisfactoryItems.xlsx
@@ -1,57 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <x:workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crisn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C93169-E60E-4470-86CE-67AE8CC28A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="5597" yWindow="13611" windowWidth="23657" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Resumen" sheetId="5" r:id="rId1"/>
-    <sheet name="Data" sheetId="1" r:id="rId2"/>
-    <sheet name="TranslationData" sheetId="2" r:id="rId3"/>
-    <sheet name="CaptionData" sheetId="3" r:id="rId4"/>
-    <sheet name="Aggregated Metadata" sheetId="4" r:id="rId5"/>
-  </sheets>
-  <definedNames>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionID" comment="Use this function to get the Extension Id from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectCaption" comment="Use this function to get the Object Caption from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Caption",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyDisplayName" comment="Use this function to get the Company Display name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company display name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.DateLocal" comment="Use this function to get the Date (Local) from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date (Local)",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.LayoutCaption" comment="Use this function to get the Layout caption from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout caption",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.LayoutId" comment="Use this function to get the Layout id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.LayoutName" comment="Use this function to get the Layout name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UTCOffset" comment="Use this function to get the UTC Offset from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("UTC Offset",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId6"/>
-  </pivotCaches>
-</workbook>
+  <x:bookViews>
+    <x:workbookView xWindow="5597" yWindow="13611" windowWidth="23657" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Resumen" sheetId="5" r:id="rId1"/>
+    <x:sheet name="Data" sheetId="1" r:id="rId2"/>
+    <x:sheet name="TranslationData" sheetId="2" r:id="rId3"/>
+    <x:sheet name="CaptionData" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Aggregated Metadata" sheetId="4" r:id="rId5"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionID" comment="Use this function to get the Extension Id from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectCaption" comment="Use this function to get the Object Caption from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Caption",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyDisplayName" comment="Use this function to get the Company Display name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company display name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.DateLocal" comment="Use this function to get the Date (Local) from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date (Local)",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.LayoutCaption" comment="Use this function to get the Layout caption from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout caption",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.LayoutId" comment="Use this function to get the Layout id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.LayoutName" comment="Use this function to get the Layout name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UTCOffset" comment="Use this function to get the UTC Offset from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("UTC Offset",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="3" r:id="rId6"/>
+  </x:pivotCaches>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
